--- a/docs/dominio-metrico/migracion/cuestionarios/el-magico-prodigioso.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/el-magico-prodigioso.xlsx
@@ -21,25 +21,25 @@
     <t>Migración métrica · El mágico prodigioso</t>
   </si>
   <si>
-    <t>Para Emma González Mesas · generado el 2026-09-19</t>
-  </si>
-  <si>
-    <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, con este mismo texto. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
-  </si>
-  <si>
-    <t>En Responder están las preguntas que no hemos podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta. Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato. Las preguntas que se refieren a cada estrofa aparecen de dos maneras: si son pocas estrofas, hay una fila por estrofa; si son muchas, hay una sola fila cuya respuesta vale para todas, y las estrofas que se aparten de ella se anotan en «Excepciones / detalle» indicando los versos y la respuesta, por ejemplo «191–194: Cruzada · abab; 203–206: Cruzada · abab».</t>
-  </si>
-  <si>
-    <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiremos a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
-  </si>
-  <si>
-    <t>En Confirmar aparecen las respuestas que hemos rellenado nosotros a partir del término que elegiste en su día: la asonancia de un romance, el esquema de una octava real «regular», o que un endecasílabo suelto «puro» no lleva pareados. Solo hay que revisarlas. Si alguna no es así, elige «No es así» y escribe al lado lo que corresponde.</t>
+    <t>Para Emma González Mesas · generado el 2026-09-20</t>
+  </si>
+  <si>
+    <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, donde estás ahora. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
+  </si>
+  <si>
+    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta. Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato. Las preguntas que se refieren a cada estrofa aparecen de dos maneras: si son pocas estrofas, hay una fila por estrofa; si son muchas, hay una sola fila cuya respuesta vale para todas, y las estrofas que se aparten de ella se anotan en «Excepciones / detalle» indicando los versos y la respuesta, por ejemplo «191–194: Cruzada · abab; 203–206: Cruzada · abab».</t>
+  </si>
+  <si>
+    <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiré a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
+  </si>
+  <si>
+    <t>En Confirmar aparecen las respuestas que he rellenado yo a partir del término que elegiste en su día: la asonancia de un romance, el esquema de una octava real «regular», o que un endecasílabo suelto «puro» no lleva pareados. Solo hay que revisarlas. Si alguna no es así, elige «No es así» y escribe al lado lo que corresponde.</t>
   </si>
   <si>
     <t>En Desviaciones están los versos hipométricos e hipermétricos, las rimas defectuosas y las lagunas que anotaste, con tus notas, y cómo quedan en el modelo nuevo. Se trasladan tal cual. Si tienes a mano el número de sílabas de algún verso hipométrico o hipermétrico, ponlo en la columna «Sílabas»; si no, se registra simplemente que el verso tiene menos o más sílabas de las que le tocan, sin dar una cifra.</t>
   </si>
   <si>
-    <t>Si algo no está claro o no sabes cómo contestarlo, pregúntaselo a David antes de dejarlo a medias. Una vez hecha la migración podrás ver cada secuencia de tu obra con el editor nuevo en el dashboard y corregir allí lo que haga falta.</t>
+    <t>Si algo no está claro o no sabes cómo contestarlo, pregúntamelo antes de dejarlo a medias. Una vez hecha la migración podrás ver cada secuencia de tu obra con el editor nuevo en el dashboard y comprobar allí que la migración no dejó ningún hueco.</t>
   </si>
   <si>
     <t>Cuando no hay desplegable, los formatos son estos:</t>

--- a/docs/dominio-metrico/migracion/cuestionarios/el-magico-prodigioso.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/el-magico-prodigioso.xlsx
@@ -33,10 +33,10 @@
     <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiré a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
   </si>
   <si>
-    <t>En Confirmar aparecen las respuestas que he rellenado yo a partir del término que elegiste en su día: la asonancia de un romance, el esquema de una octava real «regular», o que un endecasílabo suelto «puro» no lleva pareados. Solo hay que revisarlas. Si alguna no es así, elige «No es así» y escribe al lado lo que corresponde.</t>
-  </si>
-  <si>
-    <t>En Desviaciones están los versos hipométricos e hipermétricos, las rimas defectuosas y las lagunas que anotaste, con tus notas, y cómo quedan en el modelo nuevo. Se trasladan tal cual. Si tienes a mano el número de sílabas de algún verso hipométrico o hipermétrico, ponlo en la columna «Sílabas»; si no, se registra simplemente que el verso tiene menos o más sílabas de las que le tocan, sin dar una cifra.</t>
+    <t>En Confirmar aparecen las respuestas que he rellenado yo a partir del término que elegiste en su día: la asonancia de un romance, el esquema de una octava real «regular», o que un endecasílabo suelto «puro» no lleva pareados. Ahí van también los tramos que vuelven a ser una sola secuencia. Solo hay que revisarlas. Si alguna no es así, elige «No es así» y escribe al lado lo que corresponde.</t>
+  </si>
+  <si>
+    <t>En Desviaciones están los versos hipométricos e hipermétricos, las rimas defectuosas y las lagunas que anotaste, con tus notas, y cómo quedan en el modelo nuevo. Se trasladan tal cual, así que basta con revisarlas: la columna «¿Correcto?» tiene el mismo desplegable que la pestaña anterior y solo hay que tocarla si algo no queda como digo. La columna «Sílabas del verso» es únicamente para los versos hipométricos e hipermétricos, por si tienes a mano cuántas sílabas mide el verso; si no la rellenas, se registra que tiene menos o más de las que le tocan, sin dar una cifra. En las demás filas esa celda está apagada.</t>
   </si>
   <si>
     <t>Si algo no está claro o no sabes cómo contestarlo, pregúntamelo antes de dejarlo a medias. Una vez hecha la migración podrás ver cada secuencia de tu obra con el editor nuevo en el dashboard y comprobar allí que la migración no dejó ningún hueco.</t>
@@ -372,10 +372,10 @@
     <t>Cómo queda</t>
   </si>
   <si>
-    <t>Sílabas</t>
-  </si>
-  <si>
-    <t>Informativa</t>
+    <t>Sílabas del verso</t>
+  </si>
+  <si>
+    <t>Revisar</t>
   </si>
   <si>
     <t>2190–2200</t>
@@ -1857,7 +1857,7 @@
     <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="44" customWidth="1"/>
     <col min="6" max="6" width="40" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
     <col min="9" max="9" width="30" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
@@ -2025,6 +2025,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="H2:H5">
+      <formula1>Listas!$C$2:$C$3</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/dominio-metrico/migracion/cuestionarios/el-magico-prodigioso.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/el-magico-prodigioso.xlsx
@@ -21,7 +21,7 @@
     <t>Migración métrica · El mágico prodigioso</t>
   </si>
   <si>
-    <t>Para Emma González Mesas · generado el 2026-09-20</t>
+    <t>Para Emma González Mesas · generado el 2026-09-21</t>
   </si>
   <si>
     <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, donde estás ahora. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
@@ -126,7 +126,7 @@
     <t>Quintilla · Octosílaba consonante</t>
   </si>
   <si>
-    <t>El subtipo 2277–2279 tiene 3 versos, cuando una estrofa de esta forma tiene 5. En ese punto hay anotada una laguna (2277–2279). Si los 2 versos que faltan no se contaron en la numeración, la estrofa iría de 2277 a 2281 y todo lo que viene después se desplazaría 2 versos.</t>
+    <t>El subtipo 2277–2279 tiene 3 versos, cuando una estrofa de esta forma tiene 5. En ese punto hay anotada una laguna (2277–2279). Si los 2 versos que faltan no se contaron en la numeración, la estrofa iría de 2277 a 2281 y todo lo que viene después se desplazaría 2 versos. Las preguntas que dependen de cómo se reparta en estrofas te las haré cuando esto esté claro.</t>
   </si>
   <si>
     <t/>

--- a/docs/dominio-metrico/migracion/cuestionarios/el-magico-prodigioso.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/el-magico-prodigioso.xlsx
@@ -126,7 +126,7 @@
     <t>Quintilla · Octosílaba consonante</t>
   </si>
   <si>
-    <t>El subtipo 2277–2279 tiene 3 versos, cuando una estrofa de esta forma tiene 5. En ese punto hay anotada una laguna (2277–2279). Si los 2 versos que faltan no se contaron en la numeración, la estrofa iría de 2277 a 2281 y todo lo que viene después se desplazaría 2 versos. Las preguntas que dependen de cómo se reparta en estrofas te las haré cuando esto esté claro.</t>
+    <t>El subtipo 2277–2279 tiene 3 versos, cuando una estrofa de esta forma tiene 5. En ese punto hay anotada una laguna (2277–2279). Si los 2 versos que faltan no se contaron en la numeración, la estrofa iría de 2277 a 2281 y todo lo que viene después se desplazaría 2 versos.</t>
   </si>
   <si>
     <t/>

--- a/docs/dominio-metrico/migracion/cuestionarios/el-magico-prodigioso.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/el-magico-prodigioso.xlsx
@@ -27,7 +27,7 @@
     <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, donde estás ahora. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
   </si>
   <si>
-    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta. Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato. Las preguntas que se refieren a cada estrofa aparecen de dos maneras: si son pocas estrofas, hay una fila por estrofa; si son muchas, hay una sola fila cuya respuesta vale para todas, y las estrofas que se aparten de ella se anotan en «Excepciones / detalle» indicando los versos y la respuesta, por ejemplo «191–194: Cruzada · abab; 203–206: Cruzada · abab».</t>
+    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta, también cuando la pregunta es de cada estrofa: se contesta una vez y la respuesta vale para todas, y las estrofas que se aparten se anotan en «Excepciones / detalle» como «versos: esquema», por ejemplo «191-194: abab; 203-206: abab». Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato.</t>
   </si>
   <si>
     <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiré a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
@@ -54,7 +54,7 @@
     <t>Esquema de rima: una letra por verso, en mayúscula si el verso es de arte mayor y un guion si queda suelto. Por ejemplo, «aBab-B».</t>
   </si>
   <si>
-    <t>Excepciones: los versos de la estrofa y la respuesta que le corresponde, separando cada estrofa con punto y coma. Por ejemplo, «191–194: Cruzada · abab; 203–206: Cruzada · abab».</t>
+    <t>Excepciones: los versos de la estrofa y su esquema, separados por dos puntos, y cada estrofa de la siguiente con punto y coma. Por ejemplo, «191-194: abab; 203-206: abab». El esquema se escribe como arriba: una letra por verso, en mayúscula si el verso es de arte mayor.</t>
   </si>
   <si>
     <t>lista</t>
@@ -147,7 +147,7 @@
     <t>Versificación irregular</t>
   </si>
   <si>
-    <t>El término «irregular» no dice qué arquitectura de «Versificación irregular» es. Indica cuál.</t>
+    <t>El término «irregular» no dice qué arquitectura de «Versificación irregular» es. Indica cuál; las demás preguntas de este pasaje van debajo.</t>
   </si>
   <si>
     <t>Elige en el desplegable</t>
@@ -156,7 +156,7 @@
     <t>A|3835e214-e184-405a-9bae-4ccaf273e008</t>
   </si>
   <si>
-    <t>Medida de cada verso</t>
+    <t>Medida de cada verso · del mismo pasaje, sea cual sea su arquitectura</t>
   </si>
   <si>
     <t>Escribe el número de sílabas de cada verso, en orden y separados por espacios («7 11 7 7 11»)</t>
@@ -165,7 +165,7 @@
     <t>Q|3835e214-e184-405a-9bae-4ccaf273e008|Medida de cada verso</t>
   </si>
   <si>
-    <t>Esquema de rima observado</t>
+    <t>Esquema de rima observado · del mismo pasaje, sea cual sea su arquitectura</t>
   </si>
   <si>
     <t>Escribe una letra por verso, en mayúscula si es de arte mayor y un guion si el verso queda suelto («aBab-B»)</t>

--- a/docs/dominio-metrico/migracion/cuestionarios/el-magico-prodigioso.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/el-magico-prodigioso.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="172">
   <si>
     <t>Migración métrica · El mágico prodigioso</t>
   </si>
@@ -27,7 +27,7 @@
     <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, donde estás ahora. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
   </si>
   <si>
-    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta, también cuando la pregunta es de cada estrofa: se contesta una vez y la respuesta vale para todas, y las estrofas que se aparten se anotan en «Excepciones / detalle» como «versos: esquema», por ejemplo «191-194: abab; 203-206: abab». Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato.</t>
+    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta, también cuando la pregunta es de cada estrofa: se contesta una vez y la respuesta vale para todas, y las estrofas que se aparten se anotan en «Excepciones / detalle». Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» dice el formato y da un ejemplo.</t>
   </si>
   <si>
     <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiré a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
@@ -40,21 +40,6 @@
   </si>
   <si>
     <t>Si algo no está claro o no sabes cómo contestarlo, pregúntamelo antes de dejarlo a medias. Una vez hecha la migración podrás ver cada secuencia de tu obra con el editor nuevo en el dashboard y comprobar allí que la migración no dejó ningún hueco.</t>
-  </si>
-  <si>
-    <t>Cuando no hay desplegable, los formatos son estos:</t>
-  </si>
-  <si>
-    <t>Medidas: el número de sílabas de cada verso, en orden y separados por espacios. Por ejemplo, «7 11 7 7 11 7 11 11».</t>
-  </si>
-  <si>
-    <t>Posiciones: en qué versos de la estrofa cae el quebrado y cuántas sílabas tiene cada uno, separados por comas. Por ejemplo, «3: 4, 8: 5» quiere decir que el verso 3 tiene cuatro sílabas y el 8 tiene cinco.</t>
-  </si>
-  <si>
-    <t>Esquema de rima: una letra por verso, en mayúscula si el verso es de arte mayor y un guion si queda suelto. Por ejemplo, «aBab-B».</t>
-  </si>
-  <si>
-    <t>Excepciones: los versos de la estrofa y su esquema, separados por dos puntos, y cada estrofa de la siguiente con punto y coma. Por ejemplo, «191-194: abab; 203-206: abab». El esquema se escribe como arriba: una letra por verso, en mayúscula si el verso es de arte mayor.</t>
   </si>
   <si>
     <t>lista</t>
@@ -664,14 +649,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1023,7 +1007,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
@@ -1067,31 +1051,6 @@
     <row r="9" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1110,48 +1069,48 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1176,164 +1135,164 @@
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="J1" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="G2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J2" s="6" t="s">
         <v>34</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" s="6" t="s">
         <v>40</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="E4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>48</v>
+      <c r="G4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>51</v>
+        <v>45</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1367,468 +1326,468 @@
     <col min="9" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>32</v>
+      <c r="E1" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" s="6" t="s">
         <v>56</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>63</v>
-      </c>
       <c r="E3" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>65</v>
+        <v>59</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>69</v>
+        <v>63</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="6" t="s">
         <v>70</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="6" t="s">
         <v>76</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>84</v>
+        <v>69</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>88</v>
+        <v>82</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>90</v>
+        <v>75</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>93</v>
+        <v>69</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>97</v>
+        <v>91</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>100</v>
+        <v>69</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>108</v>
+        <v>102</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>111</v>
+        <v>69</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>113</v>
+        <v>63</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -1863,164 +1822,164 @@
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>32</v>
+    <row r="1" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J2" s="6" t="s">
         <v>119</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>127</v>
-      </c>
       <c r="F3" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>127</v>
-      </c>
       <c r="F4" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>130</v>
+        <v>118</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>135</v>
+        <v>129</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -2053,39 +2012,39 @@
     <col min="11" max="11" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C1" s="5" t="s">
+      <c r="J1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>137</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2093,34 +2052,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C2" s="3">
         <v>526</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2128,34 +2087,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C3" s="3">
         <v>60</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2163,34 +2122,34 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C4" s="3">
         <v>190</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2198,34 +2157,34 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C5" s="3">
         <v>110</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2233,34 +2192,34 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C6" s="3">
         <v>146</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2268,34 +2227,34 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C7" s="3">
         <v>168</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2303,34 +2262,34 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C8" s="3">
         <v>46</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2338,34 +2297,34 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C9" s="3">
         <v>48</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E9" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>159</v>
-      </c>
       <c r="K9" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2373,34 +2332,34 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C10" s="3">
         <v>124</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2408,34 +2367,34 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C11" s="3">
         <v>60</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2443,34 +2402,34 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C12" s="3">
         <v>92</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F12" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>160</v>
-      </c>
       <c r="K12" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2478,34 +2437,34 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C13" s="3">
         <v>210</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2513,34 +2472,34 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C14" s="3">
         <v>20</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2548,34 +2507,34 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C15" s="3">
         <v>60</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2583,34 +2542,34 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C16" s="3">
         <v>168</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2618,34 +2577,34 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C17" s="3">
         <v>162</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="18" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2653,34 +2612,34 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C18" s="3">
         <v>11</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="19" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2688,34 +2647,34 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C19" s="3">
         <v>258</v>
       </c>
       <c r="D19" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="F19" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>175</v>
-      </c>
       <c r="K19" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="20" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2723,34 +2682,34 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C20" s="3">
         <v>302</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2758,34 +2717,34 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C21" s="3">
         <v>100</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="22" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2793,34 +2752,34 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C22" s="3">
         <v>282</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
